--- a/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260928.xlsx
+++ b/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260928.xlsx
@@ -2232,17 +2232,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>小野町高齢者保健福祉計画_第10期介護保険事業計画_素案_第5版_20260925.docx</t>
+          <t>小野町高齢者保健福祉計画_第10期介護保険事業計画_素案_第6版_20260928.docx</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9月25日</t>
+          <t>**9月28日**</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>未確定94箇所（町データ待ち39／協議会で設定39／決定後に記載12／見える化出力待ち4）</t>
+          <t>第6版。第4章④に見える化システムとの突合を加え、保険料のケースに見える化ケースを追加した。未確定94箇所（町データ待ち39／協議会で設定39／決定後に記載12／見える化出力待ち4）</t>
         </is>
       </c>
     </row>
@@ -2276,17 +2276,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>小野町高齢者福祉サービス推進協議会資料_第9期計画の評価と令和7年度調査結果_20260805.docx</t>
+          <t>小野町高齢者福祉サービス推進協議会資料_第9期計画の評価と令和7年度調査結果_20260928.docx</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8月5日</t>
+          <t>**9月28日**</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>協議会第1回の資料。開催日が決まり次第お出しできます</t>
+          <t>協議会第1回の資料（第2版）。年報により第9期の実績を確定させ、次回お諮りする保険料2案を明記した。開催日が決まり次第お出しできます</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260928.xlsx
+++ b/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260928.xlsx
@@ -43,7 +43,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,11 +58,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -120,9 +115,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -505,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -566,12 +558,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>当方の保険料算式に誤りが1件（調整交付金見込額の基数）。6,095円→6,048円。100円未満切上げの6,100円は不変</t>
+          <t>第10期の保険料基準額 当方6,048円／システム6,533円。切上げで6,100円（▲500円）と6,600円（据え置き）</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>おわび</t>
+          <t>決定1</t>
         </is>
       </c>
     </row>
@@ -581,10 +573,10 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>第10期の保険料基準額 当方6,048円／システム6,533円。切上げで6,100円（▲500円）と6,600円（据え置き）</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
+          <t>差の主因は令和8年度の置き方のみ。月報3か月と1か月の違い</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>決定1</t>
         </is>
@@ -596,12 +588,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>差の主因は令和8年度の置き方のみ。月報3か月と1か月の違い</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>決定1</t>
+          <t>準備基金の保有額12,000千円と繰越金144.2百万円の不整合の確認</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>決定2</t>
         </is>
       </c>
     </row>
@@ -611,12 +603,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>準備基金の保有額12,000千円と繰越金144.2百万円の不整合の確認</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>決定2</t>
+          <t>協議会第1回の開催日が未定。これが律速。令和9年2月下旬の校了が期限</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>決定3</t>
         </is>
       </c>
     </row>
@@ -626,12 +618,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>協議会第1回の開催日が未定。これが律速。令和9年2月下旬の校了が期限</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>決定3</t>
+          <t>認知症の人・家族からの意見聴取の方法が未決（認知症基本法の法定要件）</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>決定4</t>
         </is>
       </c>
     </row>
@@ -641,25 +633,10 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>認知症の人・家族からの意見聴取の方法が未決（認知症基本法の法定要件）</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>決定4</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
           <t>いただきたい資料 7件。基金運用状況調書と令和7年度決算が最優先</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>依頼</t>
         </is>
@@ -745,7 +722,7 @@
           <t>A-1（月額6,100円・第9期から▲500円）を本命に、B-1（6,600円・据え置き）を対案としてお示しします。分かれ目は令和8年度の実績をどう見るかです。当方は月報4〜6月の3か月（前年同期比0.9598）で置き、システムは1か月で置いています。12か月そろうのは令和9年5月で、それまでどちらが当たっているかは確かめられません</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr"/>
+      <c r="F2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -773,7 +750,7 @@
           <t>年報 様式4 の基金保有額は12,000千円ですが、令和4年度末の120,000千円から1桁減っています。一方で歳入歳出差引残額は令和6年度末で144,205,672円あり、繰越金として滞留しています。基金運用状況調書で実額をご確認ください。取崩実績なのか年報の入力誤りなのかで、打てる手が変わります</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr"/>
+      <c r="F3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -801,7 +778,7 @@
           <t>仕様書4(5)に回数の指定がありません。当方案は4回（第1回は資料作成済み）。第1回の開催日がまだ決まっておらず、これが決まらないとパブリックコメントと印刷の日程が引けません。令和9年2月下旬の校了は動かせない期限です</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -829,7 +806,7 @@
           <t>認知症基本法13条3項が準用する12条3項の法定要件です。記述の追加では埋まらず、策定過程そのものに関わります。協議会の委員に認知症の人又はご家族が含まれるかをご確認ください。含まれない場合は、別途の聴取の場が要ります</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -857,7 +834,7 @@
           <t>仕様書2(3)は包含を計画の構成要件と定めています。当方は分散＋対応表方式（基本的施策12項目との対応表を添える）を提案しています。独立章方式にすると章立てが変わります</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -885,7 +862,7 @@
           <t>推計は通っており、いつでも提出できる状態です。ただし提出する額と協議会にお示しする額はそろえたいので、1の決定のあとにしていただくのが筋と考えます</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -967,7 +944,7 @@
           <t>保険料（決定1・2）</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr"/>
+      <c r="F2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -995,7 +972,7 @@
           <t>保険料・財政の記述</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr"/>
+      <c r="F3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1023,7 +1000,7 @@
           <t>見込量・計画本文</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1051,7 +1028,7 @@
           <t>地域支援事業の量と費用</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1079,7 +1056,7 @@
           <t>総合事業の見込量</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1107,7 +1084,7 @@
           <t>成果指標の目標値</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1135,7 +1112,7 @@
           <t>必要利用定員総数（法117条2項1号）</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1199,21 +1176,21 @@
           <t>A-1</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>当方の算定　取崩なし</t>
         </is>
       </c>
-      <c r="C2" s="9" t="n">
+      <c r="C2" s="8" t="n">
         <v>6047.77</v>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D2" s="9" t="n">
         <v>6100</v>
       </c>
-      <c r="E2" s="9" t="n">
+      <c r="E2" s="8" t="n">
         <v>73200</v>
       </c>
-      <c r="F2" s="11" t="n">
+      <c r="F2" s="10" t="n">
         <v>-500</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -1233,16 +1210,16 @@
           <t>当方の算定　基金12,000千円を全額取崩</t>
         </is>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="C3" s="8" t="n">
         <v>5949.52</v>
       </c>
-      <c r="D3" s="9" t="n">
+      <c r="D3" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="E3" s="9" t="n">
+      <c r="E3" s="8" t="n">
         <v>72000</v>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="F3" s="10" t="n">
         <v>-600</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -1262,16 +1239,16 @@
           <t>当方の算定　第9期と同じ35,000千円を取崩</t>
         </is>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C4" s="8" t="n">
         <v>5761.21</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>5800</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="8" t="n">
         <v>69600</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="10" t="n">
         <v>-800</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1286,21 +1263,21 @@
           <t>B-1</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>見える化システム　取崩なし</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>6533.46</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>6600</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>79200</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1320,16 +1297,16 @@
           <t>見える化システム　基金12,000千円を全額取崩</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="8" t="n">
         <v>6435.16</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="8" t="n">
         <v>6500</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="8" t="n">
         <v>78000</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="10" t="n">
         <v>-100</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1349,16 +1326,16 @@
           <t>見える化システム　35,000千円を取崩</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8" t="n">
         <v>6246.76</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>6300</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>75600</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="10" t="n">
         <v>-300</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1378,16 +1355,16 @@
           <t>当方の算定　第1号被保険者負担割合24％</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="8" t="n">
         <v>6316.79</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="8" t="n">
         <v>6400</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="8" t="n">
         <v>76800</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="10" t="n">
         <v>-200</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1407,16 +1384,16 @@
           <t>システム　第1号被保険者負担割合24％</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>6823.95</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="8" t="n">
         <v>6900</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>82800</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="10" t="n">
         <v>300</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1470,19 +1447,19 @@
           <t>第1段階</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="11" t="n">
         <v>0.285</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="8" t="n">
         <v>20900</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="8" t="n">
         <v>22600</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="8" t="n">
         <v>22600</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="8" t="n">
         <v>525</v>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -1493,19 +1470,19 @@
           <t>第2段階</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="11" t="n">
         <v>0.485</v>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="8" t="n">
         <v>35600</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="8" t="n">
         <v>38500</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="8" t="n">
         <v>38500</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="8" t="n">
         <v>297</v>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -1516,19 +1493,19 @@
           <t>第3段階</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="11" t="n">
         <v>0.6850000000000001</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="8" t="n">
         <v>50200</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="8" t="n">
         <v>54300</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="8" t="n">
         <v>54300</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="8" t="n">
         <v>272</v>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -1539,19 +1516,19 @@
           <t>第4段階</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="11" t="n">
         <v>0.9</v>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="8" t="n">
         <v>65900</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="8" t="n">
         <v>71300</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="8" t="n">
         <v>71300</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="8" t="n">
         <v>434</v>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -1562,19 +1539,19 @@
           <t>第5段階</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="8" t="n">
         <v>73200</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D17" s="8" t="n">
         <v>79200</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="8" t="n">
         <v>79200</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="8" t="n">
         <v>610</v>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -1585,19 +1562,19 @@
           <t>第6段階</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="11" t="n">
         <v>1.2</v>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="8" t="n">
         <v>87900</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="8" t="n">
         <v>95100</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="8" t="n">
         <v>95100</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="8" t="n">
         <v>491</v>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -1608,19 +1585,19 @@
           <t>第7段階</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="11" t="n">
         <v>1.3</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="8" t="n">
         <v>95200</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D19" s="8" t="n">
         <v>103000</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="8" t="n">
         <v>103000</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="8" t="n">
         <v>418</v>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1631,19 +1608,19 @@
           <t>第8段階</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="11" t="n">
         <v>1.5</v>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="8" t="n">
         <v>109800</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="8" t="n">
         <v>118800</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>118800</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="8" t="n">
         <v>231</v>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1654,19 +1631,19 @@
           <t>第9段階</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="11" t="n">
         <v>1.7</v>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C21" s="8" t="n">
         <v>124500</v>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="D21" s="8" t="n">
         <v>134700</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="8" t="n">
         <v>134700</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="8" t="n">
         <v>77</v>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1677,19 +1654,19 @@
           <t>第10段階</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="11" t="n">
         <v>1.9</v>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="8" t="n">
         <v>139100</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="8" t="n">
         <v>150500</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>150500</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="8" t="n">
         <v>36</v>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1700,19 +1677,19 @@
           <t>第11段階</t>
         </is>
       </c>
-      <c r="B23" s="12" t="n">
+      <c r="B23" s="11" t="n">
         <v>2.1</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="8" t="n">
         <v>153800</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="8" t="n">
         <v>166400</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="8" t="n">
         <v>166400</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="8" t="n">
         <v>14</v>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1723,19 +1700,19 @@
           <t>第12段階</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n">
+      <c r="B24" s="11" t="n">
         <v>2.3</v>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" s="8" t="n">
         <v>168400</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="8" t="n">
         <v>182200</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>182200</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="8" t="n">
         <v>7</v>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1746,19 +1723,19 @@
           <t>第13段階</t>
         </is>
       </c>
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="11" t="n">
         <v>2.4</v>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="8" t="n">
         <v>175700</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="8" t="n">
         <v>190100</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="8" t="n">
         <v>190100</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="8" t="n">
         <v>31</v>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1769,11 +1746,11 @@
           <t>合計</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9" t="n">
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n">
         <v>3443</v>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1813,7 +1790,7 @@
           <t>介護給付費準備基金 保有額（令和7年度末）</t>
         </is>
       </c>
-      <c r="B30" s="9" t="n">
+      <c r="B30" s="8" t="n">
         <v>12000000</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1836,7 +1813,7 @@
           <t>歳入歳出差引残額（令和6年度末）</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n">
+      <c r="B31" s="8" t="n">
         <v>144205672</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1859,7 +1836,7 @@
           <t>第9期の取崩額</t>
         </is>
       </c>
-      <c r="B32" s="9" t="n">
+      <c r="B32" s="8" t="n">
         <v>35000000</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2154,7 +2131,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>推計の結果と当方の算定との突合。算式の訂正を含む</t>
+          <t>推計の結果と当方の算定との突合</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2175,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>見込量と保険料の算定確定メモ（訂正を反映して作り直し済み）</t>
+          <t>見込量と保険料の算定確定メモ</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2450,17 +2427,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>おわびと訂正（当方の保険料算式）</t>
+          <t>保険料の選択肢</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>5分</t>
+          <t>**30分**</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>調整交付金見込額の基数の取りこぼし。100円未満切上げ後の額は変わりません</t>
+          <t>A案6,100円（▲500円）とB案6,600円（据え置き）。準備基金の残高の確認を含む</t>
         </is>
       </c>
     </row>
@@ -2472,17 +2449,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>保険料の選択肢</t>
+          <t>決めていただきたいこと（6件）</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>**25分**</t>
+          <t>**20分**</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>A案6,100円（▲500円）とB案6,600円（据え置き）。準備基金の残高の確認を含む</t>
+          <t>保険料・基金・協議会日程・認知症の意見聴取・認知症計画の形式・見える化の提出時期</t>
         </is>
       </c>
     </row>
@@ -2494,17 +2471,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>決めていただきたいこと（6件）</t>
+          <t>いただきたい資料（7件）</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>**20分**</t>
+          <t>10分</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>保険料・基金・協議会日程・認知症の意見聴取・認知症計画の形式・見える化の提出時期</t>
+          <t>基金運用状況調書・令和7年度決算・認定者数の計上方法ほか</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2493,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>いただきたい資料（7件）</t>
+          <t>今後の工程</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2526,7 +2503,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>基金運用状況調書・令和7年度決算・認定者数の計上方法ほか</t>
+          <t>令和9年2月下旬の校了から逆算します</t>
         </is>
       </c>
     </row>
@@ -2538,37 +2515,15 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>今後の工程</t>
+          <t>その他・次回の日程</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10分</t>
+          <t>5分</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>令和9年2月下旬の校了から逆算します</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>その他・次回の日程</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>5分</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>―</t>
         </is>

--- a/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260928.xlsx
+++ b/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260928.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -633,10 +633,55 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>いただきたい資料 7件。基金運用状況調書と令和7年度決算が最優先</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
+          <t>（改修版）総合事業ワークシートにより、小野町が訪問型サービスB・通所型サービスB（住民主体）を実施していることが判明</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>報告</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>同ワークシートは、生産年齢人口の減少により2030年に従前相当サービスの供給が需要に追いつかなくなると示す。第10期の見込量の変更は不要</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>報告</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>総合事業費の政令上の上限額が未確認。町の手引きファイルが要る</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>決定7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>いただきたい資料 10件。基金運用状況調書・令和7年度決算・総合事業上限額算定の手引きが最優先</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>依頼</t>
         </is>
@@ -653,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -864,6 +909,62 @@
       </c>
       <c r="F7" s="6" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>多様なサービス・活動（サービスB）を第10期で広げるか</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>11月の協議会まで</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>町</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>9月28日に受領した「（改修版）総合事業の充実に向けたワークシート」により、小野町が訪問型サービスB・通所型サービスB（住民主体）を実施していることが分かりました。これまで実施の有無が確認できていなかったものです。広げる場合、総合事業費を令和6年度実績の据え置きのままとするか、上乗せするかを決める必要があります。ワークシートは、生産年齢人口の減少により2030年には従前相当サービスの供給が需要に追いつかなくなると示しており、多様なサービス・活動の必要性が高まります</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>介護予防ケアマネジメントB・Cを導入するか</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>素案の確定まで</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>町</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>現在はAのみで、B・Cは実施していないと国の調査に回答されています。令和6年8月5日の地域支援事業実施要綱等の改正により、B・Cはケアプラン作成等の一部を省略・簡略化できるようになりました。地域包括支援センターの事務負担を減らせます</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -875,7 +976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1113,6 +1214,90 @@
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>総合事業上限額算定の手引き（Excel）</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>至急</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>平成27年度〜令和6年度の各年度分。総合事業費には介護保険法施行令第37条の13第4項による上限額があり、第10期の見込みが上限内に収まるかを確かめられていません。国・県への毎年度の報告に使われたものです</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>総合事業費の上限額の確認</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>地域支援事業交付金事業実績報告書（Excel）</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>至急</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>平成27年度〜令和6年度の各年度分。様式1（地域支援事業交付金精算書）を含むもの。訪問型・通所型のサービス・活動別の事業費を確かめるために要ります</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>サービス・活動別の事業費</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>総合事業の実施状況調査への回答の控え</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>10月中</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>平成29年度〜令和6年度。国の集計では、従前相当サービスの利用者数がほとんど空欄で、実人数と延べ人数が同じ年があり、サービスBの人数が408人→24人→150人→24人と激しく振れています。町の控えと突き合わせて、どちらが正しいかを確かめたい</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>多様なサービス・活動の実績</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2060,7 +2245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2330,6 +2515,50 @@
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t>作業64件・加重進捗率60.7％</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>小野町_総合事業ワークシートの確認結果_20260928.docx</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>**9月28日**</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>9月28日受領の「（改修版）総合事業の充実に向けたワークシート」の確認。サービスBの実施が判明したこと、人材の供給制約、総合事業費の上限額</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>小野町_総合事業ワークシート_小野町のデータ_20260928.xlsx</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>**9月28日**</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>同上の計数編。将来推計人口・調整済み軽度認定率・実施状況調査の回答</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2661,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>**30分**</t>
+          <t>**25分**</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -2449,12 +2678,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>決めていただきたいこと（6件）</t>
+          <t>決めていただきたいこと（8件）</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>**20分**</t>
+          <t>**25分**</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -2471,7 +2700,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>いただきたい資料（7件）</t>
+          <t>いただきたい資料（10件）</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">

--- a/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260928.xlsx
+++ b/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260928.xlsx
@@ -698,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -965,6 +965,90 @@
       </c>
       <c r="F9" s="6" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>介護給付適正化計画の位置づけ（案A・B・C）</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>素案の確定まで</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>町・協議会</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>介護保険法第117条第5項は市町村介護給付適正化計画を定めることを求めていますが、第9期計画はその名称では置いていません。当方は案B（第4章 基本目標3① の中に主要3事業の毎年度の定量的な目標を掲げる）をお勧めし、素案にはその形で記載しています。案A（独立した節）・案C（別冊）もお示しします</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>ケアプラン点検の点検件数の目標</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>11月の協議会まで</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>町</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>令和8年度交付金で唯一0点の項目です。実施していないのではなく、実施割合が全保険者の下位3割にあることによる0点です。点検件数は対象者数×点検対象月数で数えます。町内の居宅介護支援事業所3か所について、事業所あたりの件数と点検する月数をお決めいただくと目標として書けます</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>在宅医療・介護連携の4つの場面ごとの目指すべき姿</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>素案の確定まで</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>町・関係機関</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>在宅医療・在宅介護連携（支援Ⅲ）は55点で、8つの目標のうち唯一、全国平均を下回っています。評価指標は、①日常の療養支援、②入退院支援、③急変時の対応、④看取りの4つの場面ごとに目指すべき姿を設定することを求めています。素案 第4章 基本目標2⑦ に案を置きました。公立小野町地方綜合病院・田村郡医師会等との調整が要ります</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -976,7 +1060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1298,6 +1382,90 @@
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>令和6年度のケアプラン点検の実施件数</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>10月中</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>令和8年度交付金で唯一0点の項目です。件数が少ないことによるものか、報告していないことによるものかで、打てる手が変わります。点検を行った事業所数・対象者数・点検対象とした月数がわかるもの</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>決定10（点検件数の目標）</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>要介護認定の適正化の実施の内容</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>10月中</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>交付金では「3事業の全てを実施している」として得点しています。認定調査の委託の有無と件数、点検の実施状況、軽重度変更率・認定調査項目別の選択状況の分析の有無をご教示ください</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>主要3事業の定量的な目標</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>令和8年度交付金の該当状況調査票の控え</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>10月中</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>体制・取組指標群の多くは、分析結果や課題分析を「資料（記録）として作成・整理できている」ことを評価の条件にしています。得点した項目の根拠資料が残っているかを確かめたうえで、第10期計画の記載を置きます</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>計画の記載（交付金の68点の維持）</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2245,7 +2413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2404,7 +2572,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>第6版。第4章④に見える化システムとの突合を加え、保険料のケースに見える化ケースを追加した。未確定94箇所（町データ待ち39／協議会で設定39／決定後に記載12／見える化出力待ち4）</t>
+          <t>第6版。第4章④に見える化システムとの突合を加え、保険料のケースに見える化ケースを追加した。第4章 基本目標2に「⑦ 在宅医療・介護連携の推進」を新設し、基本目標3① の介護給付適正化の記述を令和8年度交付金の実際の得点に合わせて訂正した。未確定114箇所（協議会で設定54／町データ待ち42／決定後に記載12／見える化出力待ち6）</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2682,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>作業64件・加重進捗率60.7％</t>
+          <t>作業64件・加重進捗率61.3％</t>
         </is>
       </c>
     </row>
@@ -2559,6 +2727,50 @@
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t>同上の計数編。将来推計人口・調整済み軽度認定率・実施状況調査の回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>小野町_給付適正化と交付金の取りまとめ_20260928.docx</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>**9月28日**</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>9月28日受領の令和8年度交付金 該当状況調査票集計表（市町村分）及び評価指標による。537点／800点・全国平均を82点上回る。適正化は強み。最大の弱点は在宅医療・在宅介護連携</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>小野町_給付適正化と交付金_20260928.xlsx</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>**9月28日**</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>同上の計数編。指標別の得点・0点の項目・伸びしろ</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2639,7 +2851,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>10分</t>
+          <t>5分</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -2678,7 +2890,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>決めていただきたいこと（8件）</t>
+          <t>決めていただきたいこと（11件）</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -2688,7 +2900,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>保険料・基金・協議会日程・認知症の意見聴取・認知症計画の形式・見える化の提出時期</t>
+          <t>保険料・基金・協議会日程・認知症の意見聴取・認知症計画の形式・見える化の提出時期・給付適正化計画の位置づけ</t>
         </is>
       </c>
     </row>
@@ -2700,17 +2912,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>いただきたい資料（10件）</t>
+          <t>交付金の取りまとめ</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10分</t>
+          <t>5分</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>基金運用状況調書・令和7年度決算・認定者数の計上方法ほか</t>
+          <t>537点／800点。適正化は強み。弱点は在宅医療・在宅介護連携</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2934,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>今後の工程</t>
+          <t>いただきたい資料（13件）</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2732,7 +2944,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>令和9年2月下旬の校了から逆算します</t>
+          <t>基金運用状況調書・令和7年度決算・認定者数の計上方法ほか</t>
         </is>
       </c>
     </row>
@@ -2744,15 +2956,37 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>今後の工程</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>令和9年2月下旬の校了から逆算します</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>その他・次回の日程</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>5分</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>―</t>
         </is>

--- a/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260928.xlsx
+++ b/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260928.xlsx
@@ -2672,17 +2672,17 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小野町_業務進捗管理表_高齢者_20260915.xlsx</t>
+          <t>小野町_業務進捗管理表_高齢者_20260928.xlsx</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9月15日</t>
+          <t>**9月28日**</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>作業64件・加重進捗率61.3％</t>
+          <t>作業68件・加重進捗率67.1％。見える化の入力完了・総合事業ワークシート・交付金の取りまとめを反映し、作業を4件加えた（総合事業の実施状況／総合事業費の上限額／給付適正化計画の位置づけ／在宅医療連携の目指すべき姿）</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260928.xlsx
+++ b/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260928.xlsx
@@ -1060,7 +1060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1466,6 +1466,62 @@
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>介護給付費適正化方策と、その評価指標を定めた文書</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>至急</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>第9期計画本文には、主要3事業の記載はありますが「取組の効果を検証するための評価指標」の記載がありません。交付金の指標1イ（8点）の根拠となっている文書をご教示ください。別の文書がないのであれば、第10期計画に定量目標を書くことで根拠を作ることになります</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>決定9（位置づけ）・交付金32点の維持</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>広域連合分の該当状況調査票集計表</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>随時</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>受領したのは市町村分のみです。国の公表順位の母数は広域連合を含む1,741保険者であり、市町村分1,536の中での順位（258位）は公表順位ではありません</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>交付金の取りまとめ（順位の記載）</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2934,7 +2990,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>いただきたい資料（13件）</t>
+          <t>いただきたい資料（15件）</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">

--- a/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260928.xlsx
+++ b/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260928.xlsx
@@ -932,7 +932,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>9月28日に受領した「（改修版）総合事業の充実に向けたワークシート」により、小野町が訪問型サービスB・通所型サービスB（住民主体）を実施していることが分かりました。これまで実施の有無が確認できていなかったものです。広げる場合、総合事業費を令和6年度実績の据え置きのままとするか、上乗せするかを決める必要があります。ワークシートは、生産年齢人口の減少により2030年には従前相当サービスの供給が需要に追いつかなくなると示しており、多様なサービス・活動の必要性が高まります</t>
+          <t>9月28日に受領した「（改修版）総合事業の充実に向けたワークシート」により、小野町に訪問型サービスB・通所型サービスB（住民主体）の担い手が各1団体あることが分かりました（国の実施状況調査で令和元年度〜令和3年度に「実施の有無＝有」と回答され、市町村内の事業所数は平成29年度から令和4年度まで各1）。ただし令和4年度以降の実施の有無は無回答で、令和5年度の利用者数は訪問型B 24人・通所型B 0人です。まず現在の実施状況をご確認ください（依頼資料14）。広げる場合、総合事業費を令和6年度実績の据え置きのままとするか、上乗せするかを決める必要があります。ワークシートは、生産年齢人口の減少により2030年には従前相当サービスの供給が需要に追いつかなくなると示しており、多様なサービス・活動の必要性が高まります</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr"/>
@@ -1060,7 +1060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1475,22 +1475,22 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>介護給付費適正化方策と、その評価指標を定めた文書</t>
+          <t>訪問型サービスB・通所型サービスBの実態</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>至急</t>
+          <t>10月中</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>第9期計画本文には、主要3事業の記載はありますが「取組の効果を検証するための評価指標」の記載がありません。交付金の指標1イ（8点）の根拠となっている文書をご教示ください。別の文書がないのであれば、第10期計画に定量目標を書くことで根拠を作ることになります</t>
+          <t>実施団体・活動内容・参加者数・委託の有無・現在も実施しているか。国の調査では令和3年度を最後に実施の有無が無回答で、令和5年度の通所型Bの利用者数は0人です。第10期で広げるか（決定7）の前提になります</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>決定9（位置づけ）・交付金32点の維持</t>
+          <t>決定7（サービスBの拡充）・第4章 基本目標1</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr"/>
@@ -1503,25 +1503,81 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>介護給付費適正化方策と、その評価指標を定めた文書</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>至急</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>第9期計画本文には、主要3事業の記載はありますが「取組の効果を検証するための評価指標」の記載がありません。交付金の指標1イ（8点）の根拠となっている文書をご教示ください。別の文書がないのであれば、第10期計画に定量目標を書くことで根拠を作ることになります</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>決定9（位置づけ）・交付金32点の維持</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護の実績が0になった経緯</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>10月中</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>令和3年度14件・令和4年度10件・令和5年度1件と減って、令和6・7年度は0件です。事業所の休廃止によるものか、利用が他のサービスに移ったのかで、第10期の見込量の置き方が変わります</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>見込量（地域密着型サービス）</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
           <t>広域連合分の該当状況調査票集計表</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>随時</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>受領したのは市町村分のみです。国の公表順位の母数は広域連合を含む1,741保険者であり、市町村分1,536の中での順位（258位）は公表順位ではありません</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>交付金の取りまとめ（順位の記載）</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2628,7 +2684,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>第6版。第4章④に見える化システムとの突合を加え、保険料のケースに見える化ケースを追加した。第4章 基本目標2に「⑦ 在宅医療・介護連携の推進」を新設し、基本目標3① の介護給付適正化の記述を令和8年度交付金の実際の得点に合わせて訂正した。未確定114箇所（協議会で設定54／町データ待ち42／決定後に記載12／見える化出力待ち6）</t>
+          <t>第6版。第4章④に見える化システムとの突合を加え、保険料のケースに見える化ケースを追加した。第4章 基本目標2に「⑦ 在宅医療・介護連携の推進」を新設し、基本目標3① の介護給付適正化の記述を令和8年度交付金の実際の得点に合わせて訂正した。未確定115箇所（協議会で設定54／町データ待ち43／決定後に記載12／見える化出力待ち6）</t>
         </is>
       </c>
     </row>
@@ -2990,7 +3046,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>いただきたい資料（15件）</t>
+          <t>いただきたい資料（17件）</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">

--- a/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260928.xlsx
+++ b/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20260928.xlsx
@@ -1060,7 +1060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1559,25 +1559,53 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>見える化システム「要介護認定率」の県内比較の出力</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>10月中</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>成果品で「認定率は県内でも高い方にある」としている裏づけです。当方の手元にあるのは小野町の値（性・年齢調整後の地域差指数1.24）と令和7年3月末の県内2位までで、令和8年3月末の県内順位の出力がありません。見える化の地域別画面（B4系）の出力でお願いします</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>第2章3（全国・県内との比較）</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>広域連合分の該当状況調査票集計表</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>随時</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>受領したのは市町村分のみです。国の公表順位の母数は広域連合を含む1,741保険者であり、市町村分1,536の中での順位（258位）は公表順位ではありません</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>交付金の取りまとめ（順位の記載）</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3046,7 +3074,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>いただきたい資料（17件）</t>
+          <t>いただきたい資料（18件）</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
